--- a/docs/tech/ezEKP/인사연동_뷰테이블_정의서.xlsx
+++ b/docs/tech/ezEKP/인사연동_뷰테이블_정의서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\ezEKP\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="89">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>상위부서 ID (최상위 부서인 회사의 경우 NULL)</t>
+  </si>
+  <si>
+    <t>dept_name_en</t>
+  </si>
+  <si>
+    <t>부서명 영문</t>
   </si>
 </sst>
 </file>
@@ -760,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F18"/>
+  <dimension ref="B4:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
@@ -862,65 +868,78 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
-      <c r="B15" t="s">
+    <row r="16" spans="2:6">
+      <c r="B16" t="s">
         <v>85</v>
-      </c>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="C16" s="6"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="8" t="s">
         <v>79</v>
       </c>
     </row>
